--- a/claimsignal_prospects.xlsx
+++ b/claimsignal_prospects.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,14 @@
       <sz val="10"/>
     </font>
     <font>
+      <color rgb="00276221"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="009C0006"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="002F5496"/>
       <sz val="14"/>
@@ -59,7 +67,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +98,18 @@
         <bgColor rgb="003D2B1A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -116,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,16 +147,22 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -517,6 +543,9 @@
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="35" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -580,6 +609,21 @@
           <t>Why Now</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Email Format Valid</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Domain MX Valid</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Verified At</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -640,6 +684,21 @@
           <t>Rapid multi-state expansion exposes claim-tracking gaps that a structured intelligence platform would immediately close.</t>
         </is>
       </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -700,6 +759,21 @@
           <t>Franchisee network scaling creates urgent need for centralized claim intelligence to maintain brand consistency.</t>
         </is>
       </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -760,6 +834,21 @@
           <t>Hiring surge for claims staff signals process pain; ClaimSignal replaces headcount with intelligence.</t>
         </is>
       </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -820,6 +909,21 @@
           <t>Florida's post-hurricane surge is overwhelming manual adjuster workflows — friction scoring would cut adjuster re-inspection rates.</t>
         </is>
       </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -880,6 +984,21 @@
           <t>California wildfire caseload spike demands audit-ready documentation — ClaimSignal's evidence pipeline fits exactly.</t>
         </is>
       </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -940,6 +1059,21 @@
           <t>Tech-forward firm already investing in SaaS tooling; ClaimSignal supplements their client-facing brand with backend intelligence.</t>
         </is>
       </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1000,6 +1134,21 @@
           <t>Rapid office expansion means inconsistent claim documentation standards — ClaimSignal creates uniformity across locations.</t>
         </is>
       </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1060,6 +1209,21 @@
           <t>Southeast expansion into high-storm markets creates immediate need for claim friction and adjuster intelligence.</t>
         </is>
       </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -1120,6 +1284,21 @@
           <t>Commercial large-loss claims have complex supplement cycles — ClaimSignal's Scope Delta and Escalation engines add direct value.</t>
         </is>
       </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1180,6 +1359,21 @@
           <t>FEMA deployment volumes create adjuster bottlenecks that lifecycle phase tracking and escalation architecture directly solve.</t>
         </is>
       </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1240,6 +1434,21 @@
           <t>Acquisition-driven growth requires a unifying data layer — ClaimSignal's multi-org architecture fits their consulting federation model.</t>
         </is>
       </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1300,14 +1509,29 @@
           <t>Franchise network depends on predictable claim outcomes; ClaimSignal's intelligence layer standardizes performance across all units.</t>
         </is>
       </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -1360,14 +1584,29 @@
           <t>Legacy firm investing in modernization — ClaimSignal positions as the intelligence layer for a tech-forward rebrand.</t>
         </is>
       </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -1420,14 +1659,29 @@
           <t>Part of Neighborly's service franchise portfolio scaling nationally — claim intel helps franchisees compete on outcome quality.</t>
         </is>
       </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -1480,14 +1734,29 @@
           <t>High-value commercial claims in NYC require airtight documentation — PII-protected audit trails are a direct differentiator.</t>
         </is>
       </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -1540,14 +1809,29 @@
           <t>Mold and air quality claims have long supplement cycles; escalation modeling gives adjusters fewer comebacks.</t>
         </is>
       </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -1600,14 +1884,29 @@
           <t>US network scale creates data blind spots across crews — ClaimSignal's org-level dashboards unify claim performance.</t>
         </is>
       </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -1660,14 +1959,29 @@
           <t>Commercial tornado/weather claims have unpredictable supplement cycles — outcome migration scoring helps forecast settlements.</t>
         </is>
       </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -1720,14 +2034,29 @@
           <t>Regulatory complexity in PNW requires documented adjuster behavior trails — ClaimSignal's audit log is a compliance asset.</t>
         </is>
       </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -1780,14 +2109,29 @@
           <t>SE homeowner-focused brand benefits from PII-protected claim dashboards that strengthen client trust.</t>
         </is>
       </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -1840,14 +2184,29 @@
           <t>Gulf Coast hail season 2026 creating claims surge — real-time friction scoring accelerates adjuster triage.</t>
         </is>
       </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -1900,14 +2259,29 @@
           <t>Engineering opinions on property claims are only as strong as the behavioral data behind them — ClaimSignal provides that layer.</t>
         </is>
       </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -1960,14 +2334,29 @@
           <t>High-value mountain-region claims with complex moisture and mold scopes need structured supplementing tools.</t>
         </is>
       </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2020,14 +2409,29 @@
           <t>PNW moisture claims are high-supplement and high-friction — friction scoring gives owners leverage in carrier negotiations.</t>
         </is>
       </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2080,14 +2484,29 @@
           <t>Tornado season 2026 claim surge needs structured intake — ClaimSignal's evidence pipeline replaces spreadsheet chaos.</t>
         </is>
       </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -2140,14 +2559,29 @@
           <t>Hail-season surge requires fast claim triage — escalation architecture would cut the time from intake to settlement offer.</t>
         </is>
       </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2200,14 +2634,29 @@
           <t>Fire/smoke claims are high-friction with carriers — friction scoring turns anecdotal knowledge into defensible data.</t>
         </is>
       </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -2260,14 +2709,29 @@
           <t>Causation investigations feed directly into supplement and denial decisions — lifecycle phase tracking integrates naturally.</t>
         </is>
       </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -2320,14 +2784,29 @@
           <t>US property division serves contractors and consultants who need behavioral analytics to supplement carrier data.</t>
         </is>
       </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -2380,14 +2859,29 @@
           <t>Solo PA firms competing with larger firms need an intelligence edge — Founding Partner tier at $99/mo is accessible.</t>
         </is>
       </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -2440,14 +2934,29 @@
           <t>Regulatory consulting firms increasingly need audit-ready claim documentation to advise contractor clients defensively.</t>
         </is>
       </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>Tier 2</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -2500,14 +3009,29 @@
           <t>Litigation-support practice needs structured event timelines — ClaimSignal's intelligence events map directly to legal discovery.</t>
         </is>
       </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2560,14 +3084,29 @@
           <t>Enterprise scale means divisional adoption is realistic even without top-down mandate — target a regional VP first.</t>
         </is>
       </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2620,14 +3159,29 @@
           <t>Individual franchise owners inside Paul Davis are independent decision-makers — target them directly not corporate.</t>
         </is>
       </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2680,14 +3234,29 @@
           <t>Large-loss commercial claims are high-value and high-complexity — structured lifecycle tracking is a margin-protection tool.</t>
         </is>
       </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2740,14 +3309,29 @@
           <t>Franchisee owners operate as independent businesses — high volume of property claims with limited analytics support.</t>
         </is>
       </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="55" customHeight="1">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -2800,14 +3384,29 @@
           <t>Boutique Florida PA firms need differentiation post-Ian/Idalia — behavioral analytics is a client-retention story.</t>
         </is>
       </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -2860,14 +3459,29 @@
           <t>Appraisal firms involved in dispute resolution need claim behavior data to support umpire positions.</t>
         </is>
       </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -2920,14 +3534,29 @@
           <t>Engineering firms supporting contractor supplement claims need data trails — ClaimSignal provides the behavioral context.</t>
         </is>
       </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="55" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -2980,14 +3609,29 @@
           <t>Hurricane season start means claim intake is about to spike — ClaimSignal onboarding now gets ahead of the surge.</t>
         </is>
       </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="55" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -3040,14 +3684,29 @@
           <t>Ice dam and fire claims in cold climates have high supplement frequency — friction scoring adds negotiating leverage.</t>
         </is>
       </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55" customHeight="1">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -3100,14 +3759,29 @@
           <t>Solo PAs compete on outcomes — ClaimSignal's Founding Partner tier gives a solo operator enterprise-grade claim intelligence.</t>
         </is>
       </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>Public Adjuster</t>
         </is>
@@ -3160,14 +3834,29 @@
           <t>Social-media-forward PA brand can showcase ClaimSignal dashboards as a client transparency differentiator.</t>
         </is>
       </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Restoration Contractor</t>
         </is>
@@ -3220,14 +3909,29 @@
           <t>Individual franchise owners have budget autonomy and the same claim pain as independent contractors.</t>
         </is>
       </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="55" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -3280,14 +3984,29 @@
           <t>Vendor management teams inside Sedgwick influence contractor software decisions — a pilot conversation is low-risk.</t>
         </is>
       </c>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>Tier 3</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>Insurance Consulting</t>
         </is>
@@ -3338,6 +4057,21 @@
       <c r="L47" s="3" t="inlineStr">
         <is>
           <t>Managed repair networks need contractor performance data — ClaimSignal's adjuster aggregated metrics are a natural fit.</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
         </is>
       </c>
     </row>
@@ -3352,7 +4086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3360,7 +4094,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ClaimSignal B2B Prospect List — Summary</t>
         </is>
@@ -3368,12 +4102,12 @@
       <c r="B1" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -3447,6 +4181,66 @@
       </c>
       <c r="B12" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>— Email &amp; Domain Verification —</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Email Format Valid</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Email Format Invalid (flagged)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Domains MX Valid</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Domains MX Invalid (flagged)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Verified At (UTC)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-06-04T22:18:12Z</t>
+        </is>
       </c>
     </row>
   </sheetData>
